--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:23:50+00:00</t>
+    <t>2026-07-16T16:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:43:53+00:00</t>
+    <t>2026-07-17T14:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:17:21+00:00</t>
+    <t>2026-07-17T14:28:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:28:25+00:00</t>
+    <t>2026-07-17T14:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:42:22+00:00</t>
+    <t>2026-07-17T14:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:54:36+00:00</t>
+    <t>2026-07-17T15:17:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:17:10+00:00</t>
+    <t>2026-07-17T16:00:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T16:00:35+00:00</t>
+    <t>2026-07-17T16:24:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T16:24:34+00:00</t>
+    <t>2026-07-20T15:36:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:36:44+00:00</t>
+    <t>2026-07-21T07:57:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T07:57:42+00:00</t>
+    <t>2026-07-21T10:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T10:14:45+00:00</t>
+    <t>2026-07-21T13:18:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:18:49+00:00</t>
+    <t>2026-07-21T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:50:16+00:00</t>
+    <t>2026-07-21T14:27:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T14:27:28+00:00</t>
+    <t>2026-07-21T15:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:58:42+00:00</t>
+    <t>2026-07-21T16:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:45:23+00:00</t>
+    <t>2026-07-21T16:55:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:55:55+00:00</t>
+    <t>2026-07-21T17:13:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T17:13:36+00:00</t>
+    <t>2026-07-22T08:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:39:40+00:00</t>
+    <t>2026-07-22T09:49:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:49:06+00:00</t>
+    <t>2026-07-22T14:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:20:38+00:00</t>
+    <t>2026-07-22T16:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T16:56:03+00:00</t>
+    <t>2026-07-23T09:49:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:49:05+00:00</t>
+    <t>2026-07-23T12:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T12:12:23+00:00</t>
+    <t>2026-07-23T13:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T13:40:37+00:00</t>
+    <t>2026-07-23T14:54:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:54:12+00:00</t>
+    <t>2026-07-23T15:33:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:33:14+00:00</t>
+    <t>2026-07-23T15:36:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:36:41+00:00</t>
+    <t>2026-07-23T15:39:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:39:52+00:00</t>
+    <t>2026-07-23T15:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:53:35+00:00</t>
+    <t>2026-07-23T16:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:12:35+00:00</t>
+    <t>2026-07-23T16:29:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:29:41+00:00</t>
+    <t>2026-07-24T15:35:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T15:35:35+00:00</t>
+    <t>2026-07-27T09:03:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:03:27+00:00</t>
+    <t>2026-07-27T09:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-SourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:57:22+00:00</t>
+    <t>2026-07-28T09:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
